--- a/test_doc/new_org/syllabus_6_mathematics.xlsx
+++ b/test_doc/new_org/syllabus_6_mathematics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Knowing Our Numbers</t>
+          <t>Ratio and Proportion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comparing large numbers</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -461,102 +461,112 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Estimation</t>
+          <t>Unitary method</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Whole Numbers</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Roman numerals</t>
+          <t>Number line</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Properties of operations</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Types of fractions</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Whole Numbers</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Number line</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Term 1</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Properties of operations</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operations on fractions</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Playing with Numbers</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Factors and multiples</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Term 1</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Divisibility rules</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>HCF and LCM</t>
+          <t>Simple equations</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Basic Geometrical Ideas</t>
+          <t>Mensuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Points, lines and curves</t>
+          <t>Perimeter</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -564,14 +574,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Polygons and circles</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -581,211 +591,101 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Integers</t>
+          <t>Knowing Our Numbers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Negative numbers</t>
+          <t>Comparing large numbers</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operations on integers</t>
+          <t>Estimation</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fractions</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Types of fractions</t>
+          <t>Roman numerals</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Decimals</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Place value in decimals</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Term 2</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Operations on fractions</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>5</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Decimals</t>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Place value</t>
+          <t>Operations on decimals</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="inlineStr">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Multiplication and Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Multiplying big numbers</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Term 2</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Operations on decimals</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Handling</t>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pictographs</t>
+          <t>Long division</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bar graphs</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mensuration</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Perimeter</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Algebra</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Variables</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Simple equations</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Ratio and Proportion</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Unitary method</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
